--- a/KNK업무시스템구축_엑셀/V2/02_자동화_완제품/KNK_자동화_완제품_소프트웨어팀_입력_2026.xlsx
+++ b/KNK업무시스템구축_엑셀/V2/02_자동화_완제품/KNK_자동화_완제품_소프트웨어팀_입력_2026.xlsx
@@ -1279,7 +1279,7 @@
       </c>
       <c r="C7" s="8" t="inlineStr">
         <is>
-          <t>M-260105-4</t>
+          <t>M-260105-3</t>
         </is>
       </c>
       <c r="D7" s="8" t="inlineStr">
@@ -1332,7 +1332,7 @@
       </c>
       <c r="C8" s="12" t="inlineStr">
         <is>
-          <t>M-260105-5</t>
+          <t>M-260105-4</t>
         </is>
       </c>
       <c r="D8" s="12" t="inlineStr">
@@ -1438,7 +1438,7 @@
       </c>
       <c r="C10" s="12" t="inlineStr">
         <is>
-          <t>M-260105-6</t>
+          <t>M-260105-5</t>
         </is>
       </c>
       <c r="D10" s="12" t="inlineStr">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="C11" s="8" t="inlineStr">
         <is>
-          <t>M-260105-8</t>
+          <t>M-260105-7</t>
         </is>
       </c>
       <c r="D11" s="8" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="C12" s="12" t="inlineStr">
         <is>
-          <t>M-260323-3</t>
+          <t>M-260323-2</t>
         </is>
       </c>
       <c r="D12" s="12" t="inlineStr">
@@ -1597,7 +1597,7 @@
       </c>
       <c r="C13" s="8" t="inlineStr">
         <is>
-          <t>M-260105-7</t>
+          <t>M-260105-6</t>
         </is>
       </c>
       <c r="D13" s="8" t="inlineStr">
@@ -1703,7 +1703,7 @@
       </c>
       <c r="C15" s="8" t="inlineStr">
         <is>
-          <t>M-260323-2</t>
+          <t>M-260323-1</t>
         </is>
       </c>
       <c r="D15" s="8" t="inlineStr">
@@ -1866,7 +1866,7 @@
       </c>
       <c r="C18" s="12" t="inlineStr">
         <is>
-          <t>M-260320-2</t>
+          <t>M-260320-1</t>
         </is>
       </c>
       <c r="D18" s="12" t="inlineStr">
@@ -1919,7 +1919,7 @@
       </c>
       <c r="C19" s="8" t="inlineStr">
         <is>
-          <t>M-260320-3</t>
+          <t>M-260320-2</t>
         </is>
       </c>
       <c r="D19" s="8" t="inlineStr">
@@ -1972,7 +1972,7 @@
       </c>
       <c r="C20" s="12" t="inlineStr">
         <is>
-          <t>M-260320-4</t>
+          <t>M-260320-3</t>
         </is>
       </c>
       <c r="D20" s="12" t="inlineStr">
@@ -2025,7 +2025,7 @@
       </c>
       <c r="C21" s="8" t="inlineStr">
         <is>
-          <t>M-260320-5</t>
+          <t>M-260320-4</t>
         </is>
       </c>
       <c r="D21" s="8" t="inlineStr">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="C23" s="8" t="inlineStr">
         <is>
-          <t>M-251224-2</t>
+          <t>M-251224-1</t>
         </is>
       </c>
       <c r="D23" s="8" t="inlineStr">
@@ -2290,7 +2290,7 @@
       </c>
       <c r="C26" s="12" t="inlineStr">
         <is>
-          <t>M-260105-2</t>
+          <t>M-260105-1</t>
         </is>
       </c>
       <c r="D26" s="12" t="inlineStr">
